--- a/assets/downloads/AX1S-Cloud-Tagging-Taxonomie-Template.xlsx
+++ b/assets/downloads/AX1S-Cloud-Tagging-Taxonomie-Template.xlsx
@@ -7,10 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Tagging Taxonomie" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Instructies" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Introductie" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tagging Taxonomie" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Introductie'!$A$1:$G$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tagging Taxonomie'!$A$4:$E$20</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,29 +30,64 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="000B0D16"/>
-      <sz val="16"/>
+      <sz val="22"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <i val="1"/>
+      <name val="Calibri"/>
+      <color rgb="00555555"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000070F3"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000070F3"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00222222"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="00555555"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000B0D16"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000B0D16"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <sz val="10"/>
+      <name val="Calibri"/>
+      <color rgb="00222222"/>
+      <sz val="10.5"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -63,7 +101,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00EAF1FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF9DB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F9FC"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,38 +130,54 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00D5DCE8"/>
       </left>
       <right style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00D5DCE8"/>
       </right>
       <top style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00D5DCE8"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00D5DCE8"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -183,6 +252,36 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="431131"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -471,422 +570,529 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000070F3"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>AX1S Infra — Cloud Tagging Taxonomie Starter</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Kopieer dit tabblad naar je eigen sheet. Vul minimaal de verplichte tags in voor al je cloud-resources. Pas kolom C (voorbeeldwaarden) aan naar jullie eigen naamgeving.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Tag-key</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Verplicht/Optioneel</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Voorbeeldwaarden</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Eigenaar</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Doel</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>team</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Verplicht</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>platform, growth, data, infra</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Team Lead</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Kostenallocatie per team</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>environment</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Verplicht</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>production, staging, development</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Platform/DevOps</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Onderscheid productie vs. test, voorkomt verrassingen in kostenrapportage</t>
-        </is>
-      </c>
+    <row r="1" ht="8" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>project</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Verplicht</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>projectnaam of Jira-epic</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Product Owner</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Kostenallocatie per project/initiatief</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>owner</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Verplicht</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>e-mailadres of teamnaam</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Resource-eigenaar</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Wie aanspreken bij opruimen of onduidelijkheid</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>cost-center</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Optioneel</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>finance kostenplaatscode</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Koppeling met financiële administratie/grootboek</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>application</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Optioneel</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>naam van de applicatie/service</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>Granulaire kostenallocatie binnen een team</t>
-        </is>
-      </c>
-    </row>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Tagging Taxonomie Starter</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Een kant-en-klare tagging-structuur om cloud-, SaaS- en AI-resources consistent te labelen — de basis voor betrouwbare kostenallocatie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1"/>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>lifecycle</t>
-        </is>
-      </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Optioneel</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>temporary, permanent</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Resource-eigenaar</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Signaleert resources die na een periode opgeruimd moeten worden</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>data-classification</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Optioneel</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>public, internal, confidential</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Security/Compliance</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Compliance- en beveiligingsbeleid, vaak gecombineerd met kostenbeheer</t>
+          <t>Hoe gebruik je dit sjabloon?</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr"/>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="5" t="inlineStr"/>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="inlineStr"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>1.</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Ga naar het tabblad “Tagging Taxonomie”.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr"/>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="5" t="inlineStr"/>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr"/>
-      <c r="B15" s="5" t="inlineStr"/>
-      <c r="C15" s="5" t="inlineStr"/>
-      <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="5" t="inlineStr"/>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Daar staan 8 aanbevolen starter-tags, al ingevuld.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr"/>
-      <c r="B16" s="5" t="inlineStr"/>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>2.</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Begin met de tags gemarkeerd “Verplicht”.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr"/>
-      <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr"/>
-      <c r="B18" s="5" t="inlineStr"/>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-    </row>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Dit zijn de 4 tags die de meeste FinOps-teams als absolute basis gebruiken.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Pas kolom C (voorbeeldwaarden) aan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Vervang de voorbeelden door jullie eigen teamnamen, omgevingen en projectstructuur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>4.</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Dwing de verplichte tags af.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Via Infrastructure-as-Code policies, cloud-provider tag policies, of een lichte handmatige review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>5.</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Herzie de taxonomie elk kwartaal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Nieuwe teams of projecten vragen soms om een aanpassing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Meer nodig dan dit sjabloon?</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="34" customHeight="1">
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>AX1S Infra helpt SaaS, fintech en digital-first bedrijven structureel besparen op cloud-, SaaS- en AI-kosten. Gratis intake: ax1s-infra.com/#contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+  <mergeCells count="15">
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="B8:F9"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="B30:F31"/>
+    <mergeCell ref="C14:F14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000070F3"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Hoe gebruik je deze tagging-taxonomie?</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>1. Begin met de 4 'Verplicht'-tags (team, environment, project, owner). Dit zijn de tags die de meeste FinOps-teams als absolute basis gebruiken voor kostenallocatie.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>2. Pas de voorbeeldwaarden in kolom C aan naar jullie eigen teamnamen, omgevingen en projectstructuur.</t>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Cloud Tagging Taxonomie</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Geel gemarkeerde cellen zijn bedoeld om aan te passen naar jullie eigen situatie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Tag-key</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>Verplicht/Optioneel</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>Voorbeeldwaarden</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>Eigenaar</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>Doel</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>3. Dwing de verplichte tags af bij het aanmaken van nieuwe resources — via Infrastructure-as-Code policies, cloud-provider tag policies, of een lichte handmatige review.</t>
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Verplicht</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>platform, growth, data, infra</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>Team Lead</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>Kostenallocatie per team</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>4. Voeg optionele tags toe zodra jullie basis staat. Begin niet met te veel tags tegelijk — dat werkt averechts.</t>
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>environment</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Verplicht</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>production, staging, development</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>Platform/DevOps</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>Onderscheid productie vs. test, voorkomt verrassingen in kostenrapportage</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>5. Herzie de taxonomie elk kwartaal: nieuwe teams of projecten vragen soms om een aanpassing.</t>
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>project</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Verplicht</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>projectnaam of Jira-epic</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Product Owner</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Kostenallocatie per project/initiatief</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr"/>
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Verplicht</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>e-mailadres of teamnaam</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>Resource-eigenaar</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>Wie aanspreken bij opruimen of onduidelijkheid</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Geel gemarkeerde cellen op het eerste tabblad zijn bedoeld om aan te passen.</t>
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>cost-center</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Optioneel</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>finance kostenplaatscode</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Koppeling met financiële administratie/grootboek</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr"/>
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>application</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>Optioneel</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>naam van de applicatie/service</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>Granulaire kostenallocatie binnen een team</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Vragen over tagging of FinOps in het algemeen? AX1S Infra helpt SaaS, fintech en digital-first bedrijven structureel besparen op cloud-, SaaS- en AI-kosten.</t>
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>lifecycle</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Optioneel</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>temporary, permanent</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Resource-eigenaar</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Signaleert resources die na een periode opgeruimd moeten worden</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Gratis intake: https://ax1s-infra.com/#contact</t>
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>data-classification</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>Optioneel</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>public, internal, confidential</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>Security/Compliance</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>Compliance- en beveiligingsbeleid, vaak gecombineerd met kostenbeheer</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Meer gratis tools: https://ax1s-infra.com/</t>
-        </is>
-      </c>
+      <c r="A13" s="16" t="inlineStr"/>
+      <c r="B13" s="16" t="inlineStr"/>
+      <c r="C13" s="16" t="inlineStr"/>
+      <c r="D13" s="16" t="inlineStr"/>
+      <c r="E13" s="16" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr"/>
+      <c r="B14" s="16" t="inlineStr"/>
+      <c r="C14" s="16" t="inlineStr"/>
+      <c r="D14" s="16" t="inlineStr"/>
+      <c r="E14" s="16" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr"/>
+      <c r="B15" s="16" t="inlineStr"/>
+      <c r="C15" s="16" t="inlineStr"/>
+      <c r="D15" s="16" t="inlineStr"/>
+      <c r="E15" s="16" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr"/>
+      <c r="B16" s="16" t="inlineStr"/>
+      <c r="C16" s="16" t="inlineStr"/>
+      <c r="D16" s="16" t="inlineStr"/>
+      <c r="E16" s="16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr"/>
+      <c r="B17" s="16" t="inlineStr"/>
+      <c r="C17" s="16" t="inlineStr"/>
+      <c r="D17" s="16" t="inlineStr"/>
+      <c r="E17" s="16" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr"/>
+      <c r="B18" s="16" t="inlineStr"/>
+      <c r="C18" s="16" t="inlineStr"/>
+      <c r="D18" s="16" t="inlineStr"/>
+      <c r="E18" s="16" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr"/>
+      <c r="B19" s="16" t="inlineStr"/>
+      <c r="C19" s="16" t="inlineStr"/>
+      <c r="D19" s="16" t="inlineStr"/>
+      <c r="E19" s="16" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr"/>
+      <c r="B20" s="16" t="inlineStr"/>
+      <c r="C20" s="16" t="inlineStr"/>
+      <c r="D20" s="16" t="inlineStr"/>
+      <c r="E20" s="16" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1"/>
+  <autoFilter ref="A4:E20"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="B5:B20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Verplicht,Optioneel"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>